--- a/data/trans_orig/IP74A6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP74A6_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19273</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26959</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24833</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34282</t>
+          <t>35450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>41980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61566</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112359</t>
+          <t>112531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
